--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/avg/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/avg/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -762,6 +762,117 @@
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>dice_p=50,ash_p=None,react_th=None,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>90.93000000000001</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>91.01000000000001</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=50,ash_p=None,react_th=None,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>93.31</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>91.86</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>93.38</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=0.1,type=avg</t>
         </is>
       </c>
     </row>
